--- a/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
@@ -440,52 +440,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>47.41570643695313</v>
+        <v>43.33044465028649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,25 +505,25 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="F2" t="n">
-        <v>48.54888232601961</v>
+        <v>39.35277315025178</v>
       </c>
       <c r="G2" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="H2" t="n">
-        <v>49.61574802954139</v>
+        <v>41.06140880269356</v>
       </c>
       <c r="I2" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="J2" t="n">
-        <v>49.02314144</v>
+        <v>42.82857448095045</v>
       </c>
       <c r="K2" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>54.52178950627489</v>
+        <v>85.27568745251914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,25 +542,25 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="F3" t="n">
-        <v>52.12772892361605</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="G3" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="H3" t="n">
-        <v>54.67251192146596</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="I3" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="J3" t="n">
-        <v>53.18119774117862</v>
+        <v>85.14350582583329</v>
       </c>
       <c r="K3" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
     </row>
     <row r="4">
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>59.67149179695313</v>
+        <v>85.27568745251914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,25 +579,25 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="F4" t="n">
-        <v>58.93183485333952</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="G4" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="H4" t="n">
-        <v>60.65578364682359</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="I4" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="J4" t="n">
-        <v>60.65578364682359</v>
+        <v>85.14350582583329</v>
       </c>
       <c r="K4" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>77.61997394666668</v>
+        <v>87.93249336257323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,25 +616,25 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="F5" t="n">
-        <v>77.61997394666666</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="G5" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="H5" t="n">
-        <v>81.75248838390944</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="I5" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="J5" t="n">
-        <v>81.25622379304795</v>
+        <v>85.14350582583329</v>
       </c>
       <c r="K5" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>77.61997394666666</v>
+        <v>87.93249336257323</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,25 +653,25 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="F6" t="n">
-        <v>77.61997394666666</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="G6" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="H6" t="n">
-        <v>81.75248838390944</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="I6" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
       <c r="J6" t="n">
-        <v>81.25622379304794</v>
+        <v>85.14350582583329</v>
       </c>
       <c r="K6" t="n">
-        <v>31430.21288707466</v>
+        <v>31447.89763053299</v>
       </c>
     </row>
     <row r="7">
@@ -690,25 +690,25 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>47.145319330612</v>
+        <v>27.08768043244852</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>47.145319330612</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>27.07244765965853</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27.07244765965853</v>
+        <v>27.08768043244852</v>
       </c>
     </row>
     <row r="8">
@@ -727,25 +727,25 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>47.145319330612</v>
+        <v>35.02957834972923</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>47.145319330612</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>35.00987944604269</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35.00987944604269</v>
+        <v>35.02957834972923</v>
       </c>
     </row>
     <row r="9">
@@ -764,25 +764,25 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>47.145319330612</v>
+        <v>38.56644581610146</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>47.145319330612</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>38.5447579529454</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38.5447579529454</v>
+        <v>38.56644581610146</v>
       </c>
     </row>
     <row r="10">
@@ -801,25 +801,25 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>47.145319330612</v>
+        <v>40.50455689726513</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>47.145319330612</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>40.48177913621933</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40.48177913621933</v>
+        <v>40.50455689726513</v>
       </c>
     </row>
     <row r="11">
@@ -838,25 +838,25 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>47.145319330612</v>
+        <v>41.70789730676758</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>47.145319330612</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>41.6844428465451</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>41.6844428465451</v>
+        <v>41.70789730676758</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008290678331764645</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008290678331764705</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.009011606882352941</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -995,13 +995,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008878852912353481</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008850562118534539</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.009011606882352941</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.008878852912353481</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.008850562118534539</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>1.2868574628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="G17" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="I17" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J17" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="K17" t="n">
         <v>1.2868574628</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>1.2868574628</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="G18" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="I18" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J18" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="K18" t="n">
         <v>1.2868574628</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>1.2868574628</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="G19" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="I19" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J19" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="K19" t="n">
         <v>1.2868574628</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.11489798775</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1180,13 +1180,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09070376781244265</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="I20" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09370966465570502</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="K20" t="n">
         <v>1.2868574628</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.11489798775</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1217,13 +1217,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09070376781244265</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="I21" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09370966465570502</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="K21" t="n">
         <v>1.2868574628</v>
@@ -1985,7 +1985,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>3.705750567087525</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1.880046910442136</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>3.705750567087525</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2.526249092198093</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>3.705750567087525</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2.836698752917273</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>3.705750567087525</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3.01471779090852</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>3.705750567087525</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3.128725737876166</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2013398184074657</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2170,25 +2170,25 @@
         <v>0.08</v>
       </c>
       <c r="E47" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4090284304735894</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4665131908356118</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5977720877192074</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="48">
@@ -2196,7 +2196,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.8262653976142558</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
         <v>0.08</v>
       </c>
       <c r="E48" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F48" t="n">
-        <v>1.024943173328522</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8834946094221606</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J48" t="n">
-        <v>1.04756022588461</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="49">
@@ -2233,7 +2233,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.8262653976142558</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2244,25 +2244,25 @@
         <v>0.08</v>
       </c>
       <c r="E49" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F49" t="n">
-        <v>1.024943173328522</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8834946094221606</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J49" t="n">
-        <v>1.04756022588461</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="50">
@@ -2270,7 +2270,7 @@
         <v>51502</v>
       </c>
       <c r="B50" t="n">
-        <v>0.62492557920679</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2281,25 +2281,25 @@
         <v>0.08</v>
       </c>
       <c r="E50" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6159147428549328</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4169814185865489</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4497881381654028</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="51">
@@ -2318,25 +2318,25 @@
         <v>0.08</v>
       </c>
       <c r="E51" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="52">
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>0.9745343041553989</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2355,25 +2355,25 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
-        <v>9.109003245912584</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1.139805678462902</v>
       </c>
       <c r="G52" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1672466948049194</v>
+        <v>0.9647126967907047</v>
       </c>
       <c r="I52" t="n">
-        <v>2.454243728747179</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1.137324415846374</v>
       </c>
       <c r="K52" t="n">
-        <v>2.454243728747179</v>
+        <v>2.335489999936831</v>
       </c>
     </row>
     <row r="53">
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>1.038145263927251</v>
+        <v>2.873579449874479</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2392,25 +2392,25 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
-        <v>9.109003245912584</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="F53" t="n">
-        <v>1.058378259260321</v>
+        <v>2.968197968865652</v>
       </c>
       <c r="G53" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H53" t="n">
-        <v>1.242631229443763</v>
+        <v>2.846595129892914</v>
       </c>
       <c r="I53" t="n">
-        <v>3.620669583986453</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J53" t="n">
-        <v>1.049568350280087</v>
+        <v>2.973780062832532</v>
       </c>
       <c r="K53" t="n">
-        <v>3.620669583986453</v>
+        <v>3.445475894438722</v>
       </c>
     </row>
     <row r="54">
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.424446392536133</v>
+        <v>2.980312443430628</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,25 +2429,25 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
-        <v>9.109003245912584</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="F54" t="n">
-        <v>1.436570648698661</v>
+        <v>3.077189268401386</v>
       </c>
       <c r="G54" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H54" t="n">
-        <v>1.644757352233743</v>
+        <v>2.968646412586611</v>
       </c>
       <c r="I54" t="n">
-        <v>4.289432041873921</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J54" t="n">
-        <v>1.482668467366361</v>
+        <v>3.060045500198731</v>
       </c>
       <c r="K54" t="n">
-        <v>4.289432041873921</v>
+        <v>4.081878878557442</v>
       </c>
     </row>
     <row r="55">
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.191551223467769</v>
+        <v>3.198323525649897</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,25 +2466,25 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
-        <v>9.109003245912584</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="F55" t="n">
-        <v>2.1268967932664</v>
+        <v>3.332371178024898</v>
       </c>
       <c r="G55" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H55" t="n">
-        <v>2.139915467628115</v>
+        <v>3.23971841641166</v>
       </c>
       <c r="I55" t="n">
-        <v>4.719717872689544</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J55" t="n">
-        <v>2.035767947295985</v>
+        <v>3.269736036639328</v>
       </c>
       <c r="K55" t="n">
-        <v>4.719717872689544</v>
+        <v>4.491344427236824</v>
       </c>
     </row>
     <row r="56">
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.389349086047102</v>
+        <v>3.058829379926089</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,25 +2503,25 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
-        <v>9.109003245912584</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="F56" t="n">
-        <v>2.356363353515988</v>
+        <v>3.270842222678461</v>
       </c>
       <c r="G56" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H56" t="n">
-        <v>2.393154694391755</v>
+        <v>3.196804501008751</v>
       </c>
       <c r="I56" t="n">
-        <v>5.018826316393861</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J56" t="n">
-        <v>2.354388135514639</v>
+        <v>3.202184544173091</v>
       </c>
       <c r="K56" t="n">
-        <v>5.018826316393861</v>
+        <v>4.775979881729643</v>
       </c>
     </row>
     <row r="57">
@@ -2540,25 +2540,25 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
-        <v>9.109003245912584</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2.454243728747179</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2.454243728747179</v>
+        <v>2.335489999936831</v>
       </c>
     </row>
     <row r="58">
@@ -2577,25 +2577,25 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>9.109003245912584</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3.620669583986453</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>3.620669583986453</v>
+        <v>3.445475894438722</v>
       </c>
     </row>
     <row r="59">
@@ -2614,25 +2614,25 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
-        <v>9.109003245912584</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>4.289432041873921</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>4.289432041873921</v>
+        <v>4.081878878557442</v>
       </c>
     </row>
     <row r="60">
@@ -2651,25 +2651,25 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
-        <v>9.109003245912584</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>4.719717872689544</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>4.719717872689544</v>
+        <v>4.491344427236824</v>
       </c>
     </row>
     <row r="61">
@@ -2688,25 +2688,25 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
-        <v>9.109003245912584</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>5.018826316393861</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>5.018826316393861</v>
+        <v>4.775979881729643</v>
       </c>
     </row>
     <row r="62">
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3023146725285634</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2725,25 +2725,25 @@
         <v>0.08</v>
       </c>
       <c r="E62" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3023146725285632</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H62" t="n">
-        <v>0.322047023434721</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3580348213560448</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="63">
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3023146725285634</v>
+        <v>0.460493929382878</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
         <v>0.08</v>
       </c>
       <c r="E63" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3023146725285632</v>
+        <v>0.4441377190821189</v>
       </c>
       <c r="G63" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H63" t="n">
-        <v>0.322047023434721</v>
+        <v>0.4965511770593832</v>
       </c>
       <c r="I63" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3580348213560448</v>
+        <v>0.403622706582872</v>
       </c>
       <c r="K63" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="64">
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.8918743144321275</v>
+        <v>1.353760935826729</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
         <v>0.08</v>
       </c>
       <c r="E64" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8922280365446449</v>
+        <v>1.335146419546385</v>
       </c>
       <c r="G64" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8918743144321277</v>
+        <v>1.374499894365686</v>
       </c>
       <c r="I64" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8898975828370594</v>
+        <v>1.317357269216672</v>
       </c>
       <c r="K64" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="65">
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.066529616637813</v>
+        <v>1.477678059668234</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
         <v>0.08</v>
       </c>
       <c r="E65" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F65" t="n">
-        <v>1.140194883191039</v>
+        <v>1.391970342055296</v>
       </c>
       <c r="G65" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H65" t="n">
-        <v>1.136739993085692</v>
+        <v>1.484623103668534</v>
       </c>
       <c r="I65" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J65" t="n">
-        <v>1.21040703410863</v>
+        <v>1.419338927757271</v>
       </c>
       <c r="K65" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="66">
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.49365733326527</v>
+        <v>2.455052416054516</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,25 +2873,25 @@
         <v>0.08</v>
       </c>
       <c r="E66" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F66" t="n">
-        <v>1.526643065796384</v>
+        <v>2.291379508064205</v>
       </c>
       <c r="G66" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H66" t="n">
-        <v>1.470480563496041</v>
+        <v>2.365417229733916</v>
       </c>
       <c r="I66" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J66" t="n">
-        <v>1.511573362642819</v>
+        <v>2.324770630885982</v>
       </c>
       <c r="K66" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="67">
@@ -2910,25 +2910,25 @@
         <v>0.08</v>
       </c>
       <c r="E67" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="68">
@@ -2947,25 +2947,25 @@
         <v>0.08</v>
       </c>
       <c r="E68" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="69">
@@ -2984,25 +2984,25 @@
         <v>0.08</v>
       </c>
       <c r="E69" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="70">
@@ -3021,25 +3021,25 @@
         <v>0.08</v>
       </c>
       <c r="E70" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="71">
@@ -3058,25 +3058,25 @@
         <v>0.08</v>
       </c>
       <c r="E71" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="72">
@@ -3095,25 +3095,25 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>9.109003245912584</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2765063185989636</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2765063185989636</v>
+        <v>0.2631269806022396</v>
       </c>
     </row>
     <row r="73">
@@ -3132,25 +3132,25 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>9.109003245912584</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4682964947358649</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4682964947358649</v>
+        <v>0.445636986926065</v>
       </c>
     </row>
     <row r="74">
@@ -3169,25 +3169,25 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>9.109003245912584</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6165030757738437</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6165030757738437</v>
+        <v>0.5866722817847868</v>
       </c>
     </row>
     <row r="75">
@@ -3206,25 +3206,25 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7369952514719948</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7369952514719948</v>
+        <v>0.7013341909168983</v>
       </c>
     </row>
     <row r="76">
@@ -3243,25 +3243,25 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.838132233560783</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.838132233560783</v>
+        <v>0.7975774480659066</v>
       </c>
     </row>
     <row r="77">
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3280,25 +3280,25 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>9.109003245912584</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="G77" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3724014066674143</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2765063185989636</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3724014066674143</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2765063185989636</v>
+        <v>0.2631269806022396</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,25 +3317,25 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>9.109003245912584</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="G78" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4682964947358649</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J78" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4682964947358649</v>
+        <v>0.445636986926065</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>9.109003245912584</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="G79" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H79" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6165030757738437</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J79" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6165030757738437</v>
+        <v>0.5866722817847868</v>
       </c>
     </row>
     <row r="80">
@@ -3391,25 +3391,25 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H80" t="n">
-        <v>0.16999837858744</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7369952514719948</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J80" t="n">
-        <v>0.16999837858744</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7369952514719948</v>
+        <v>0.7013341909168983</v>
       </c>
     </row>
     <row r="81">
@@ -3428,25 +3428,25 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.838132233560783</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.838132233560783</v>
+        <v>0.7975774480659066</v>
       </c>
     </row>
     <row r="82">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.3003616885396124</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3003616885396124</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.4512642451846701</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4512642451846701</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.5417375857912977</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5417375857912977</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.6023565753116631</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6023565753116631</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.6461848252881226</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6461848252881226</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.3003616885396124</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3003616885396124</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.4512642451846701</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4512642451846701</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.5417375857912977</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5417375857912977</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.6023565753116631</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6023565753116631</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.6461848252881226</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6461848252881226</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.3003616885396124</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3003616885396124</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0.4512642451846701</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4512642451846701</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.5417375857912977</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5417375857912977</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.6023565753116631</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6023565753116631</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0.6461848252881226</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6461848252881226</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>

--- a/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,44 +441,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
@@ -490,11 +491,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>43.33044465028649</v>
+        <v>39.35277315025178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,13 +509,13 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F2" t="n">
-        <v>39.35277315025178</v>
+        <v>41.06140880269356</v>
       </c>
       <c r="G2" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H2" t="n">
-        <v>41.06140880269356</v>
+        <v>43.33044465028649</v>
       </c>
       <c r="I2" t="n">
         <v>31447.89763053299</v>
@@ -527,11 +528,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>85.27568745251914</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,13 +546,13 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F3" t="n">
-        <v>77.61997394666663</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="G3" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H3" t="n">
-        <v>77.61997394666665</v>
+        <v>85.27568745251914</v>
       </c>
       <c r="I3" t="n">
         <v>31447.89763053299</v>
@@ -564,11 +565,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>85.27568745251914</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,13 +583,13 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F4" t="n">
-        <v>77.61997394666663</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="G4" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H4" t="n">
-        <v>77.61997394666665</v>
+        <v>85.27568745251914</v>
       </c>
       <c r="I4" t="n">
         <v>31447.89763053299</v>
@@ -601,11 +602,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>87.93249336257323</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -625,7 +626,7 @@
         <v>31447.89763053299</v>
       </c>
       <c r="H5" t="n">
-        <v>77.61997394666665</v>
+        <v>87.93249336257323</v>
       </c>
       <c r="I5" t="n">
         <v>31447.89763053299</v>
@@ -638,11 +639,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>87.93249336257323</v>
+        <v>77.61997394666663</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,13 +657,13 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F6" t="n">
-        <v>77.61997394666663</v>
+        <v>77.61997394666665</v>
       </c>
       <c r="G6" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H6" t="n">
-        <v>77.61997394666665</v>
+        <v>87.93249336257323</v>
       </c>
       <c r="I6" t="n">
         <v>31447.89763053299</v>
@@ -675,7 +676,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -690,7 +691,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>27.08768043244852</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -702,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>47.17184644579947</v>
+        <v>27.08768043244852</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -712,7 +713,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -727,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>35.02957834972923</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -739,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>47.17184644579947</v>
+        <v>35.02957834972923</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -749,7 +750,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -764,7 +765,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>38.56644581610146</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -776,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>47.17184644579947</v>
+        <v>38.56644581610146</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -786,7 +787,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -801,7 +802,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>40.50455689726513</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -813,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>47.17184644579947</v>
+        <v>40.50455689726513</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -823,7 +824,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -838,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>41.70789730676758</v>
+        <v>47.17184644579947</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -850,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>47.17184644579947</v>
+        <v>41.70789730676758</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -860,7 +861,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -897,7 +898,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -934,7 +935,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
@@ -971,11 +972,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009011606882352941</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -995,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.009011606882352941</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1008,11 +1009,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009011606882352941</v>
+        <v>0.008651142607058822</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1032,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.009011606882352941</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1045,11 +1046,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,13 +1064,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="G17" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="I17" t="n">
         <v>1.2868574628</v>
@@ -1082,11 +1083,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,13 +1101,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="G18" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="I18" t="n">
         <v>1.2868574628</v>
@@ -1119,11 +1120,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,13 +1138,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="G19" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="I19" t="n">
         <v>1.2868574628</v>
@@ -1156,11 +1157,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1180,7 +1181,7 @@
         <v>1.2868574628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="I20" t="n">
         <v>1.2868574628</v>
@@ -1193,11 +1194,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1217,7 +1218,7 @@
         <v>1.2868574628</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="I21" t="n">
         <v>1.2868574628</v>
@@ -1230,7 +1231,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,7 +1490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1985,7 +1986,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>1.880046910442136</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1997,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3.705750567087525</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2022,7 +2023,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>2.526249092198093</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2034,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3.705750567087525</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2059,7 +2060,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>2.836698752917273</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2071,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3.705750567087525</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2096,7 +2097,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01471779090852</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2108,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3.705750567087525</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2118,7 +2119,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2133,7 +2134,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>3.128725737876166</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2145,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3.705750567087525</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2192,7 +2193,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2266,7 +2267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2340,11 +2341,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.9745343041553989</v>
+        <v>1.139805678462902</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2355,19 +2356,19 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.9647126967907047</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.9745343041553989</v>
+      </c>
+      <c r="I52" t="n">
         <v>2.335489999936831</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.139805678462902</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.9647126967907047</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J52" t="n">
         <v>1.137324415846374</v>
@@ -2377,11 +2378,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>2.873579449874479</v>
+        <v>2.968197968865652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2392,19 +2393,19 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.846595129892914</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.873579449874479</v>
+      </c>
+      <c r="I53" t="n">
         <v>3.445475894438722</v>
-      </c>
-      <c r="F53" t="n">
-        <v>2.968197968865652</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.846595129892914</v>
-      </c>
-      <c r="I53" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J53" t="n">
         <v>2.973780062832532</v>
@@ -2414,11 +2415,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.980312443430628</v>
+        <v>3.077189268401386</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,19 +2430,19 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.968646412586611</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.980312443430628</v>
+      </c>
+      <c r="I54" t="n">
         <v>4.081878878557442</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3.077189268401386</v>
-      </c>
-      <c r="G54" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2.968646412586611</v>
-      </c>
-      <c r="I54" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J54" t="n">
         <v>3.060045500198731</v>
@@ -2451,11 +2452,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>3.198323525649897</v>
+        <v>3.332371178024898</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,19 +2467,19 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.23971841641166</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.198323525649897</v>
+      </c>
+      <c r="I55" t="n">
         <v>4.491344427236824</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3.332371178024898</v>
-      </c>
-      <c r="G55" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.23971841641166</v>
-      </c>
-      <c r="I55" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J55" t="n">
         <v>3.269736036639328</v>
@@ -2488,11 +2489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>3.058829379926089</v>
+        <v>3.270842222678461</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,19 +2504,19 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.196804501008751</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.058829379926089</v>
+      </c>
+      <c r="I56" t="n">
         <v>4.775979881729643</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.270842222678461</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.196804501008751</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J56" t="n">
         <v>3.202184544173091</v>
@@ -2525,7 +2526,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,19 +2541,19 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>2.335489999936831</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2562,7 +2563,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,19 +2578,19 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>3.445475894438722</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2599,7 +2600,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,19 +2615,19 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>4.081878878557442</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2636,7 +2637,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,19 +2652,19 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>4.491344427236824</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2673,7 +2674,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,19 +2689,19 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>4.775979881729643</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2710,7 +2711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2747,11 +2748,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.460493929382878</v>
+        <v>0.4441377190821189</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,13 +2766,13 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4441377190821189</v>
+        <v>0.4965511770593832</v>
       </c>
       <c r="G63" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4965511770593832</v>
+        <v>0.460493929382878</v>
       </c>
       <c r="I63" t="n">
         <v>8.668245024336169</v>
@@ -2784,11 +2785,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.353760935826729</v>
+        <v>1.335146419546385</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,13 +2803,13 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F64" t="n">
-        <v>1.335146419546385</v>
+        <v>1.374499894365686</v>
       </c>
       <c r="G64" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H64" t="n">
-        <v>1.374499894365686</v>
+        <v>1.353760935826729</v>
       </c>
       <c r="I64" t="n">
         <v>8.668245024336169</v>
@@ -2821,11 +2822,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.477678059668234</v>
+        <v>1.391970342055296</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,13 +2840,13 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F65" t="n">
-        <v>1.391970342055296</v>
+        <v>1.484623103668534</v>
       </c>
       <c r="G65" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H65" t="n">
-        <v>1.484623103668534</v>
+        <v>1.477678059668234</v>
       </c>
       <c r="I65" t="n">
         <v>8.668245024336169</v>
@@ -2858,11 +2859,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>2.455052416054516</v>
+        <v>2.291379508064205</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,13 +2877,13 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F66" t="n">
-        <v>2.291379508064205</v>
+        <v>2.365417229733916</v>
       </c>
       <c r="G66" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H66" t="n">
-        <v>2.365417229733916</v>
+        <v>2.455052416054516</v>
       </c>
       <c r="I66" t="n">
         <v>8.668245024336169</v>
@@ -2895,7 +2896,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2932,7 +2933,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2969,7 +2970,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3006,7 +3007,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3080,7 +3081,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,19 +3096,19 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
         <v>0.2631269806022396</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3117,7 +3118,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,19 +3133,19 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
         <v>0.445636986926065</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3154,7 +3155,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,19 +3170,19 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
         <v>0.5866722817847868</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3191,7 +3192,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,19 +3207,19 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>0.7013341909168983</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3228,7 +3229,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,19 +3244,19 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
         <v>0.7975774480659066</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3265,11 +3266,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3280,19 +3281,19 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.3543819837641523</v>
+      </c>
+      <c r="I77" t="n">
         <v>0.2631269806022396</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="G77" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="I77" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J77" t="n">
         <v>0.3116721949811959</v>
@@ -3302,11 +3303,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,19 +3318,19 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.3543819837641523</v>
+      </c>
+      <c r="I78" t="n">
         <v>0.445636986926065</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="G78" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="I78" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J78" t="n">
         <v>0.3116721949811959</v>
@@ -3339,11 +3340,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,19 +3355,19 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.3543819837641523</v>
+      </c>
+      <c r="I79" t="n">
         <v>0.5866722817847868</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="I79" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J79" t="n">
         <v>0.3116721949811959</v>
@@ -3376,7 +3377,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3391,19 +3392,19 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
         <v>0.7013341909168983</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -3413,7 +3414,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,19 +3429,19 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
         <v>0.7975774480659066</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -3450,7 +3451,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3463,19 +3464,19 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.3003616885396124</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3485,7 +3486,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3498,19 +3499,19 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.4512642451846701</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3520,7 +3521,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3533,19 +3534,19 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.5417375857912977</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3555,7 +3556,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3568,19 +3569,19 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6023565753116631</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3590,7 +3591,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3603,19 +3604,19 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6461848252881226</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3625,7 +3626,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3638,19 +3639,19 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.3003616885396124</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3660,7 +3661,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3673,19 +3674,19 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.4512642451846701</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3695,7 +3696,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3708,19 +3709,19 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.5417375857912977</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3730,7 +3731,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3743,19 +3744,19 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6023565753116631</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3765,7 +3766,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3778,19 +3779,19 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6461848252881226</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3800,7 +3801,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3813,19 +3814,19 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.3003616885396124</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3835,7 +3836,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3848,19 +3849,19 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.4512642451846701</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3883,19 +3884,19 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.5417375857912977</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3905,7 +3906,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3918,19 +3919,19 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6023565753116631</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3940,7 +3941,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3953,19 +3954,19 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6461848252881226</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>

--- a/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/Hermenches_MFH_until_2004_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,31 +470,31 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>39.35277315025178</v>
+        <v>38.2118920024964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,30 +508,30 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F2" t="n">
-        <v>41.06140880269356</v>
+        <v>38.03491669181982</v>
       </c>
       <c r="G2" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H2" t="n">
-        <v>43.33044465028649</v>
+        <v>38.21189200249639</v>
       </c>
       <c r="I2" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="J2" t="n">
-        <v>42.82857448095045</v>
+        <v>38.03491669181983</v>
       </c>
       <c r="K2" t="n">
         <v>31447.89763053299</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>77.61997394666663</v>
+        <v>53.27141765707074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,30 +545,30 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F3" t="n">
-        <v>77.61997394666665</v>
+        <v>53.27141765707074</v>
       </c>
       <c r="G3" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H3" t="n">
-        <v>85.27568745251914</v>
+        <v>53.27141765707074</v>
       </c>
       <c r="I3" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="J3" t="n">
-        <v>85.14350582583329</v>
+        <v>54.93462684611799</v>
       </c>
       <c r="K3" t="n">
         <v>31447.89763053299</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>77.61997394666663</v>
+        <v>98.74558451836663</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,30 +582,30 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F4" t="n">
-        <v>77.61997394666665</v>
+        <v>103.191437703971</v>
       </c>
       <c r="G4" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H4" t="n">
-        <v>85.27568745251914</v>
+        <v>98.74558451836674</v>
       </c>
       <c r="I4" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="J4" t="n">
-        <v>85.14350582583329</v>
+        <v>101.7972992760942</v>
       </c>
       <c r="K4" t="n">
         <v>31447.89763053299</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>77.61997394666665</v>
+        <v>104.417356208186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,30 +619,30 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F5" t="n">
-        <v>77.61997394666665</v>
+        <v>104.4781238025396</v>
       </c>
       <c r="G5" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H5" t="n">
-        <v>87.93249336257323</v>
+        <v>104.9039868976714</v>
       </c>
       <c r="I5" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="J5" t="n">
-        <v>85.14350582583329</v>
+        <v>105.2844044212649</v>
       </c>
       <c r="K5" t="n">
         <v>31447.89763053299</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>77.61997394666663</v>
+        <v>104.417356208186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,26 +656,26 @@
         <v>31447.89763053299</v>
       </c>
       <c r="F6" t="n">
-        <v>77.61997394666665</v>
+        <v>104.4781238025396</v>
       </c>
       <c r="G6" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="H6" t="n">
-        <v>87.93249336257323</v>
+        <v>104.9039868976714</v>
       </c>
       <c r="I6" t="n">
         <v>31447.89763053299</v>
       </c>
       <c r="J6" t="n">
-        <v>85.14350582583329</v>
+        <v>105.2844044212649</v>
       </c>
       <c r="K6" t="n">
         <v>31447.89763053299</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -684,36 +683,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Hermenches_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Hermenches_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>27.08768043244852</v>
+        <v>0.1188028249192565</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27.08768043244852</v>
+        <v>0.1188028249192565</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -721,36 +720,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Hermenches_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Hermenches_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>35.02957834972923</v>
+        <v>0.1536348922181257</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35.02957834972923</v>
+        <v>0.1536348922181257</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -758,36 +757,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Hermenches_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Hermenches_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>38.56644581610146</v>
+        <v>0.1691471043995233</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38.56644581610146</v>
+        <v>0.1691471043995233</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -795,36 +794,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Hermenches_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Hermenches_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>40.50455689726513</v>
+        <v>0.1776473919019458</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40.50455689726513</v>
+        <v>0.1776473919019458</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -832,40 +831,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Hermenches_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Hermenches_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>47.17184644579947</v>
+        <v>0.2068892029494382</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>41.70789730676758</v>
+        <v>0.182925076727891</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>41.70789730676758</v>
+        <v>0.182925076727891</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470585</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,30 +878,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470585</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,30 +915,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470585</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,30 +952,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470597</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470585</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,30 +989,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009011606882352941</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470597</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470585</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,30 +1026,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009011606882352941</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.008651142607058822</v>
+        <v>0.007930214056470587</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.4066972391978736</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,30 +1063,30 @@
         <v>1.2868574628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.4076345394501667</v>
       </c>
       <c r="G17" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4066972391978737</v>
       </c>
       <c r="I17" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4076345394501668</v>
       </c>
       <c r="K17" t="n">
         <v>1.2868574628</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,30 +1100,30 @@
         <v>1.2868574628</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="G18" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="I18" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="K18" t="n">
         <v>1.2868574628</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1490189445946008</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,30 +1137,30 @@
         <v>1.2868574628</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1365965460824477</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="G19" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="I19" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="K19" t="n">
         <v>1.2868574628</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.3362538825190295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,30 +1174,30 @@
         <v>1.2868574628</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.3361153709787713</v>
       </c>
       <c r="G20" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.3592893458021262</v>
       </c>
       <c r="I20" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.3583520455498331</v>
       </c>
       <c r="K20" t="n">
         <v>1.2868574628</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.3383463308539388</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,26 +1211,26 @@
         <v>1.2868574628</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.3382004128356805</v>
       </c>
       <c r="G21" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.34469396325</v>
       </c>
       <c r="I21" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.34469396325</v>
       </c>
       <c r="K21" t="n">
         <v>1.2868574628</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1268,7 +1267,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1342,7 +1341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1379,7 +1378,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1416,7 +1415,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1453,7 +1452,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1490,7 +1489,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1527,7 +1526,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1564,7 +1563,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1601,7 +1600,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1675,7 +1674,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1712,7 +1711,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1749,7 +1748,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1786,7 +1785,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1860,7 +1859,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1897,7 +1896,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1934,7 +1933,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1971,7 +1970,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2008,7 +2007,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2045,7 +2044,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2082,7 +2081,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2119,7 +2118,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2156,7 +2155,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2193,7 +2192,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2230,7 +2229,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2267,7 +2266,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2341,11 +2340,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>1.139805678462902</v>
+        <v>1.23962336180346</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,30 +2358,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9647126967907047</v>
+        <v>1.022919609786701</v>
       </c>
       <c r="G52" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9745343041553989</v>
+        <v>1.243085274532566</v>
       </c>
       <c r="I52" t="n">
         <v>2.335489999936831</v>
       </c>
       <c r="J52" t="n">
-        <v>1.137324415846374</v>
+        <v>1.035931665466861</v>
       </c>
       <c r="K52" t="n">
         <v>2.335489999936831</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>2.968197968865652</v>
+        <v>2.959425936718283</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,30 +2395,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F53" t="n">
-        <v>2.846595129892914</v>
+        <v>2.844658458035571</v>
       </c>
       <c r="G53" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H53" t="n">
-        <v>2.873579449874479</v>
+        <v>2.96288784944739</v>
       </c>
       <c r="I53" t="n">
         <v>3.445475894438722</v>
       </c>
       <c r="J53" t="n">
-        <v>2.973780062832532</v>
+        <v>2.850047957587999</v>
       </c>
       <c r="K53" t="n">
         <v>3.445475894438722</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>3.077189268401386</v>
+        <v>3.005339303355403</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,30 +2432,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F54" t="n">
-        <v>2.968646412586611</v>
+        <v>2.844658458035571</v>
       </c>
       <c r="G54" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H54" t="n">
-        <v>2.980312443430628</v>
+        <v>3.011251625731855</v>
       </c>
       <c r="I54" t="n">
         <v>4.081878878557442</v>
       </c>
       <c r="J54" t="n">
-        <v>3.060045500198731</v>
+        <v>2.853257428819573</v>
       </c>
       <c r="K54" t="n">
         <v>4.081878878557442</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>3.332371178024898</v>
+        <v>3.217930792737935</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,30 +2469,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F55" t="n">
-        <v>3.23971841641166</v>
+        <v>3.190693697497855</v>
       </c>
       <c r="G55" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H55" t="n">
-        <v>3.198323525649897</v>
+        <v>3.187232003258527</v>
       </c>
       <c r="I55" t="n">
         <v>4.491344427236824</v>
       </c>
       <c r="J55" t="n">
-        <v>3.269736036639328</v>
+        <v>3.173232504592503</v>
       </c>
       <c r="K55" t="n">
         <v>4.491344427236824</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>3.270842222678461</v>
+        <v>3.221959136115379</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,26 +2506,26 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F56" t="n">
-        <v>3.196804501008751</v>
+        <v>3.193717894773948</v>
       </c>
       <c r="G56" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H56" t="n">
-        <v>3.058829379926089</v>
+        <v>3.173486991488915</v>
       </c>
       <c r="I56" t="n">
         <v>4.775979881729643</v>
       </c>
       <c r="J56" t="n">
-        <v>3.202184544173091</v>
+        <v>3.011251625731854</v>
       </c>
       <c r="K56" t="n">
         <v>4.775979881729643</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2563,7 +2562,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2600,7 +2599,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2637,7 +2636,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2674,7 +2673,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2711,7 +2710,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2748,11 +2747,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.4441377190821189</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,30 +2765,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4965511770593832</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H63" t="n">
-        <v>0.460493929382878</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="J63" t="n">
-        <v>0.403622706582872</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>8.668245024336169</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.335146419546385</v>
+        <v>0.3651362479664485</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,30 +2802,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F64" t="n">
-        <v>1.374499894365686</v>
+        <v>0.3920130017816497</v>
       </c>
       <c r="G64" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H64" t="n">
-        <v>1.353760935826729</v>
+        <v>0.3626858383191034</v>
       </c>
       <c r="I64" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="J64" t="n">
-        <v>1.317357269216672</v>
+        <v>0.4046930887357992</v>
       </c>
       <c r="K64" t="n">
         <v>8.668245024336169</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.391970342055296</v>
+        <v>0.3651362479664485</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,30 +2839,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F65" t="n">
-        <v>1.484623103668534</v>
+        <v>0.3920130017816497</v>
       </c>
       <c r="G65" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H65" t="n">
-        <v>1.477678059668234</v>
+        <v>0.392949400818234</v>
       </c>
       <c r="I65" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="J65" t="n">
-        <v>1.419338927757271</v>
+        <v>0.4046930887357992</v>
       </c>
       <c r="K65" t="n">
         <v>8.668245024336169</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>2.291379508064205</v>
+        <v>0.9874760527148405</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,26 +2876,26 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F66" t="n">
-        <v>2.365417229733916</v>
+        <v>1.015356952631393</v>
       </c>
       <c r="G66" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H66" t="n">
-        <v>2.455052416054516</v>
+        <v>1.033062560713682</v>
       </c>
       <c r="I66" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="J66" t="n">
-        <v>2.324770630885982</v>
+        <v>1.195699313958054</v>
       </c>
       <c r="K66" t="n">
         <v>8.668245024336169</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2933,7 +2932,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2970,7 +2969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3007,7 +3006,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3044,7 +3043,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3081,7 +3080,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3108,17 +3107,17 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2631269806022396</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2631269806022396</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3145,17 +3144,17 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.445636986926065</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.445636986926065</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3182,17 +3181,17 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5866722817847868</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5866722817847868</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3219,17 +3218,17 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7013341909168983</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7013341909168983</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3256,21 +3255,21 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7975774480659066</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7975774480659066</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.312005832132422</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,30 +3283,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3811952131278954</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="G77" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2631269806022396</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3116721949811959</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2631269806022396</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.312005832132422</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,30 +3320,30 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F78" t="n">
-        <v>0.3811952131278954</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="G78" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="I78" t="n">
-        <v>0.445636986926065</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3116721949811959</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="K78" t="n">
-        <v>0.445636986926065</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.312005832132422</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,26 +3357,26 @@
         <v>8.668245024336169</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3811952131278954</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="G79" t="n">
         <v>8.668245024336169</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3543819837641523</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5866722817847868</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3116721949811959</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5866722817847868</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3404,17 +3403,17 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7013341909168983</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7013341909168983</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3441,17 +3440,17 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7975774480659066</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7975774480659066</v>
+        <v>8.668245024336169</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3486,7 +3485,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3521,7 +3520,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3556,7 +3555,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3591,7 +3590,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3626,7 +3625,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3661,7 +3660,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3696,7 +3695,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3731,7 +3730,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3766,7 +3765,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3801,7 +3800,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3836,7 +3835,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3871,7 +3870,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3906,7 +3905,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3941,7 +3940,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
